--- a/config/yunying/grid_walk_tasks.xlsx
+++ b/config/yunying/grid_walk_tasks.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="grid_walk_tasks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grid_walk_tasks" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1236,7 +1236,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>17</t>
@@ -1247,10 +1246,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>本日ログイン</t>
+          <t>今日登录</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1263,14 +1261,11 @@
           <t>Log in today</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>{8112=3}</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1278,7 +1273,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>55</t>
@@ -1289,10 +1283,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付5回</t>
+          <t>公会捐赠5次</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1305,8 +1298,6 @@
           <t>Donate to Guild 5 times</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>{8112=1}</t>
@@ -1324,7 +1315,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>41</t>
@@ -1335,10 +1325,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>アリーナで計5回戦闘</t>
+          <t>在竞技场共计战斗5次</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1351,8 +1340,6 @@
           <t>Battle 5 times total in Arena</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>{8112=1}</t>
@@ -1370,7 +1357,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>86</t>
@@ -1388,7 +1374,7 @@
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Lv.S以上の依頼を1回クリア</t>
+          <t>完成1次Lv.S以上的请求</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1401,8 +1387,6 @@
           <t>Clear 1 Rank S or higher Dispatch</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>{8112=1}</t>
@@ -1420,7 +1404,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>30</t>
@@ -1431,10 +1414,9 @@
           <t>15</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ハードステージに15回挑戦</t>
+          <t>挑战15次困难关卡</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1447,8 +1429,6 @@
           <t>Challenge Hard Stages 15 times</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>{8112=1}</t>
@@ -1466,7 +1446,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>26</t>
@@ -1477,10 +1456,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>スタミナを2回購入</t>
+          <t>购买两次耐力</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1493,8 +1471,6 @@
           <t>Buy Stamina 2 times</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>{8112=1}</t>
@@ -1512,7 +1488,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>21</t>
@@ -1523,10 +1498,9 @@
           <t>200</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>計200ダイヤ消費</t>
+          <t>共消费200颗钻石</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1539,28 +1513,14 @@
           <t>Spend 200 total Diamonds</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>{8112=2}</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="1" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1568,17 +1528,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計1回発動</t>
+          <t>累计发动1次宝箱获得</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1591,14 +1548,11 @@
           <t>Open 1 total chest</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;5000=50;27001=5}</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1606,17 +1560,14 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計2回発動</t>
+          <t>累计发动2次宝箱获得</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1629,14 +1580,11 @@
           <t>Open 2 total chests</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;930=50;27001=5}</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1644,17 +1592,14 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計4回発動</t>
+          <t>累计发动4次宝箱获得</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1667,14 +1612,11 @@
           <t>Open 4 total chests</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;16=15;27001=5}</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1682,17 +1624,14 @@
           <t>13</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計7回発動</t>
+          <t>累计发动7次宝箱获得</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1705,14 +1644,11 @@
           <t>Open 7 total chests</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;850=100;27001=5}</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1720,17 +1656,14 @@
           <t>14</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計10回発動</t>
+          <t>累计发动10次宝箱获得</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1743,14 +1676,11 @@
           <t>Open 10 total chests</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;902=25;27001=5}</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1758,17 +1688,14 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計13回発動</t>
+          <t>累计发动13次宝箱获得</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1781,14 +1708,11 @@
           <t>Open 13 total chests</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;5000=50;27001=5}</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1796,17 +1720,14 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計16回発動</t>
+          <t>累计发动16次宝箱获得</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1819,14 +1740,11 @@
           <t>Open 16 total chests</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;930=50;27001=5}</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1834,17 +1752,14 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計18回発動</t>
+          <t>累计发动宝箱18次</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1857,14 +1772,11 @@
           <t>Open 18 total chests</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;16=15;27001=5}</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1872,17 +1784,14 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計21回発動</t>
+          <t>累计发动21次宝箱获得</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1895,14 +1804,11 @@
           <t>Open 21 total chests</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;850=50;27001=5}</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1910,17 +1816,14 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>宝箱獲得を累計25回発動</t>
+          <t>累计发动25次宝箱获得</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1933,14 +1836,11 @@
           <t>Open 25 total chests</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>{gold=300000;6393=15;902=25;27001=5}</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
